--- a/data/trans_camb/P1416-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1416-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,01</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,81</t>
+          <t>3,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 1,17</t>
+          <t>-5,36; 1,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,02</t>
+          <t>-5,11; 2,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 6,06</t>
+          <t>-1,91; 5,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 4,52</t>
+          <t>-5,37; 4,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 4,09</t>
+          <t>-5,28; 4,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 10,03</t>
+          <t>0,66; 9,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 1,79</t>
+          <t>-4,14; 1,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,02</t>
+          <t>-3,82; 2,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,59</t>
+          <t>1,01; 6,98</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 21,84</t>
+          <t>-54,82; 26,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-53,56; 37,83</t>
+          <t>-54,09; 38,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 116,81</t>
+          <t>-21,27; 92,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 57,77</t>
+          <t>-42,47; 56,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 53,93</t>
+          <t>-40,22; 56,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 137,84</t>
+          <t>3,84; 126,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 25,58</t>
+          <t>-41,73; 21,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 29,28</t>
+          <t>-37,91; 30,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,46; 96,44</t>
+          <t>9,18; 104,59</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,85</t>
+          <t>-5,74; 1,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 1,64</t>
+          <t>-5,78; 1,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 7,16</t>
+          <t>-2,18; 6,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 2,5</t>
+          <t>-7,91; 2,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,53</t>
+          <t>-8,74; 0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 3,97</t>
+          <t>-5,83; 3,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,09</t>
+          <t>-5,94; 0,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,08</t>
+          <t>-5,91; 0,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,71</t>
+          <t>-2,8; 3,49</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-6,75%</t>
+          <t>-5,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 36,02</t>
+          <t>-60,36; 33,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,38; 30,25</t>
+          <t>-60,79; 30,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 132,05</t>
+          <t>-24,51; 110,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,88; 24,51</t>
+          <t>-49,61; 22,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,9; 5,01</t>
+          <t>-52,0; 6,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 34,28</t>
+          <t>-33,56; 30,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 1,86</t>
+          <t>-47,47; 4,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,54; 1,4</t>
+          <t>-48,1; 1,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 39,58</t>
+          <t>-21,63; 38,22</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>4,6</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>7,86</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>5,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,26</t>
+          <t>-5,14; 1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 0,23</t>
+          <t>-6,17; -0,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 5,82</t>
+          <t>0,4; 8,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 6,13</t>
+          <t>-3,69; 5,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 11,08</t>
+          <t>-0,84; 10,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 13,15</t>
+          <t>2,21; 12,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,58</t>
+          <t>-3,41; 1,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,46</t>
+          <t>-3,53; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 6,85</t>
+          <t>2,42; 8,38</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>130,89%</t>
+          <t>130,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 20,42</t>
+          <t>-54,66; 22,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,16; 6,86</t>
+          <t>-67,83; -0,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,25; 84,96</t>
+          <t>2,74; 140,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 195,69</t>
+          <t>-43,94; 175,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 315,17</t>
+          <t>-14,21; 304,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,07; 369,68</t>
+          <t>20,07; 371,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 27,8</t>
+          <t>-39,81; 35,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 27,26</t>
+          <t>-42,56; 28,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 105,42</t>
+          <t>26,63; 140,33</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>1,99</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>2,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,5</t>
+          <t>-3,34; 0,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -0,62</t>
+          <t>-4,2; -0,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,18</t>
+          <t>-0,28; 4,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 1,55</t>
+          <t>-4,55; 1,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 0,68</t>
+          <t>-5,46; 0,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 2,73</t>
+          <t>-0,95; 4,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,41</t>
+          <t>-2,94; 0,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -0,54</t>
+          <t>-3,75; -0,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,32</t>
+          <t>0,49; 4,23</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,78%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,38; 11,33</t>
+          <t>-47,5; 12,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,97; -10,36</t>
+          <t>-59,15; -11,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 85,07</t>
+          <t>-6,8; 83,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 17,65</t>
+          <t>-39,39; 20,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 8,6</t>
+          <t>-45,85; 8,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,07; 28,57</t>
+          <t>-7,91; 57,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 6,01</t>
+          <t>-35,32; 4,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,16; -8,44</t>
+          <t>-45,38; -8,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 49,04</t>
+          <t>5,61; 62,56</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>4,52</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>2,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 1,48</t>
+          <t>-4,87; 1,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,6</t>
+          <t>-4,08; 1,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 9,85</t>
+          <t>0,61; 8,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -3,35</t>
+          <t>-8,99; -3,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,8; -0,21</t>
+          <t>-7,07; -0,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 2,3</t>
+          <t>-2,33; 3,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,54; -2,01</t>
+          <t>-6,71; -2,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,24</t>
+          <t>-5,35; -0,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,31</t>
+          <t>-0,28; 5,05</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105,05%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-8,9%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,71; 41,79</t>
+          <t>-63,27; 39,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 48,11</t>
+          <t>-55,03; 54,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21,01; 258,72</t>
+          <t>6,72; 225,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,6; -34,54</t>
+          <t>-71,37; -34,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 0,29</t>
+          <t>-55,49; -3,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 25,66</t>
+          <t>-18,45; 47,84</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-64,97; -27,15</t>
+          <t>-65,36; -29,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,69; -4,72</t>
+          <t>-50,11; -8,76</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 61,94</t>
+          <t>-3,18; 69,45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8,6</t>
+          <t>6,48</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 4,03</t>
+          <t>-4,6; 4,28</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 7,3</t>
+          <t>-2,18; 7,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 20,12</t>
+          <t>-0,53; 15,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,67</t>
+          <t>-3,61; 0,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,14</t>
+          <t>-3,35; 0,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,83</t>
+          <t>-2,22; 2,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,71</t>
+          <t>-3,25; 0,73</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,5</t>
+          <t>-2,39; 1,63</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 5,16</t>
+          <t>-1,01; 4,17</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112,84%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-49,83; 73,94</t>
+          <t>-49,04; 87,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 132,95</t>
+          <t>-25,0; 130,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 344,16</t>
+          <t>-11,6; 265,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 10,07</t>
+          <t>-40,95; 12,59</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 18,37</t>
+          <t>-38,0; 15,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 41,99</t>
+          <t>-25,59; 33,82</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 10,95</t>
+          <t>-36,93; 10,23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 21,91</t>
+          <t>-27,66; 22,79</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 70,74</t>
+          <t>-11,7; 58,64</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>3,05</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,59</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,45</t>
+          <t>-2,81; -0,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,59</t>
+          <t>-2,87; -0,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,52</t>
+          <t>1,69; 4,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,98</t>
+          <t>-3,51; -0,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,29</t>
+          <t>-2,95; -0,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,54</t>
+          <t>0,85; 3,52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -1,03</t>
+          <t>-2,8; -0,98</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,74</t>
+          <t>-2,54; -0,79</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,97</t>
+          <t>1,56; 3,63</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-36,78; -6,38</t>
+          <t>-37,76; -5,68</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,78; -9,54</t>
+          <t>-39,54; -8,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7,2; 74,37</t>
+          <t>21,61; 71,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,59; -10,94</t>
+          <t>-34,42; -9,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-28,83; -3,36</t>
+          <t>-29,1; -2,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 27,89</t>
+          <t>8,37; 39,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,47; -13,37</t>
+          <t>-32,71; -13,19</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-29,56; -9,86</t>
+          <t>-29,55; -10,47</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2,61; 37,82</t>
+          <t>17,57; 46,16</t>
         </is>
       </c>
     </row>
